--- a/data/trans_camb/P16A12-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,26</t>
+          <t>-3,16; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,81</t>
+          <t>-0,77; 6,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,79</t>
+          <t>0,29; 5,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,44</t>
+          <t>-0,19; 5,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,58</t>
+          <t>-0,07; 4,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,34</t>
+          <t>-0,35; 3,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,65</t>
+          <t>-1,3; 2,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,23</t>
+          <t>0,05; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,79</t>
+          <t>0,03; 3,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 66,03</t>
+          <t>-50,68; 73,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 172,74</t>
+          <t>-14,82; 167,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 170,56</t>
+          <t>5,02; 189,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 764,39</t>
+          <t>-31,12; 685,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 717,28</t>
+          <t>-15,31; 739,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 504,66</t>
+          <t>-22,7; 466,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 101,6</t>
+          <t>-31,43; 103,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 164,15</t>
+          <t>-2,64; 159,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 150,78</t>
+          <t>-0,44; 147,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,56</t>
+          <t>-2,55; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,82</t>
+          <t>-1,8; 4,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,78</t>
+          <t>1,49; 7,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,77</t>
+          <t>-0,99; 3,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,85</t>
+          <t>-0,91; 3,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,49</t>
+          <t>-0,84; 2,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,07</t>
+          <t>-0,67; 3,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,43</t>
+          <t>-0,3; 3,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,01</t>
+          <t>1,34; 5,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 115,69</t>
+          <t>-39,28; 136,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 162,15</t>
+          <t>-31,81; 148,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,12; 258,99</t>
+          <t>19,9; 255,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 710,82</t>
+          <t>-59,36; 565,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 783,97</t>
+          <t>-55,64; 675,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 452,06</t>
+          <t>-38,63; 458,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 144,68</t>
+          <t>-19,89; 149,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 166,47</t>
+          <t>-11,5; 165,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 232,35</t>
+          <t>35,46; 245,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,29</t>
+          <t>2,09; 8,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,24</t>
+          <t>1,71; 8,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,56</t>
+          <t>-3,57; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,5</t>
+          <t>-6,12; 3,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 5,33</t>
+          <t>-6,85; 4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 7,68</t>
+          <t>-2,92; 7,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,07</t>
+          <t>0,55; 5,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,17</t>
+          <t>0,56; 6,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 5,81</t>
+          <t>-3,34; 5,6</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,16; 206,92</t>
+          <t>29,88; 203,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,77; 204,68</t>
+          <t>23,63; 208,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 140,14</t>
+          <t>-60,48; 132,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,47; 79,9</t>
+          <t>-61,27; 79,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 117,08</t>
+          <t>-68,45; 101,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 188,62</t>
+          <t>-30,14; 145,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,05; 142,78</t>
+          <t>7,42; 132,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,04; 133,07</t>
+          <t>7,03; 132,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 113,24</t>
+          <t>-48,31; 103,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,99</t>
+          <t>-0,85; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,95</t>
+          <t>-0,43; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,26</t>
+          <t>0,7; 5,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,26</t>
+          <t>-1,35; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,52</t>
+          <t>-2,59; 1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,9</t>
+          <t>-3,03; 2,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,91</t>
+          <t>-0,57; 2,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,28</t>
+          <t>-0,9; 2,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,06</t>
+          <t>-1,38; 2,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 61,93</t>
+          <t>-11,05; 56,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 61,32</t>
+          <t>-4,86; 64,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 79,63</t>
+          <t>7,39; 83,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 108,25</t>
+          <t>-26,58; 91,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 53,76</t>
+          <t>-48,6; 48,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,46; 52,25</t>
+          <t>-55,0; 61,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 53,03</t>
+          <t>-7,81; 50,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 41,47</t>
+          <t>-12,33; 40,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 52,91</t>
+          <t>-17,15; 53,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,71</t>
+          <t>-3,19; 3,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,74</t>
+          <t>0,77; 7,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,74</t>
+          <t>-0,97; 5,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,55</t>
+          <t>1,05; 6,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,52</t>
+          <t>1,0; 6,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,71</t>
+          <t>1,65; 7,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,52</t>
+          <t>0,38; 4,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,48</t>
+          <t>1,87; 6,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,03</t>
+          <t>1,52; 5,96</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 85,66</t>
+          <t>-35,74; 88,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,83; 171,17</t>
+          <t>6,27; 168,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 131,47</t>
+          <t>-12,38; 126,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,18; 174,07</t>
+          <t>12,4; 174,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,1; 193,35</t>
+          <t>14,46; 171,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,95; 201,61</t>
+          <t>25,65; 192,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,71; 97,72</t>
+          <t>3,56; 107,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,37; 141,24</t>
+          <t>25,7; 147,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,24; 136,23</t>
+          <t>21,7; 131,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,63</t>
+          <t>0,38; 4,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,21</t>
+          <t>0,03; 3,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,83</t>
+          <t>-0,43; 1,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,56</t>
+          <t>1,84; 7,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,26</t>
+          <t>0,85; 6,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,73</t>
+          <t>-0,89; 3,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,74</t>
+          <t>1,34; 6,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,08</t>
+          <t>0,78; 5,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,71</t>
+          <t>-1,33; 2,63</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14,28; 76,74</t>
+          <t>15,78; 83,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,48; 71,33</t>
+          <t>7,74; 75,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 42,02</t>
+          <t>-8,3; 44,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,85; 81,41</t>
+          <t>13,49; 80,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,47; 70,52</t>
+          <t>9,51; 74,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 39,04</t>
+          <t>-15,22; 37,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,95</t>
+          <t>0,54; 2,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,08</t>
+          <t>1,51; 3,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,12</t>
+          <t>0,69; 4,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,55</t>
+          <t>1,1; 3,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,04</t>
+          <t>0,63; 3,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,94</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,94</t>
+          <t>1,18; 2,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,17</t>
+          <t>1,42; 3,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,68</t>
+          <t>0,64; 2,72</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,71; 58,4</t>
+          <t>9,52; 58,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24,78; 78,68</t>
+          <t>25,07; 76,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,43; 79,58</t>
+          <t>12,49; 79,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,08; 64,92</t>
+          <t>16,57; 70,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,62; 54,24</t>
+          <t>8,85; 58,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 34,61</t>
+          <t>-9,39; 35,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,86; 55,57</t>
+          <t>19,14; 52,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>21,38; 58,98</t>
+          <t>22,77; 57,69</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,7; 48,83</t>
+          <t>10,93; 49,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A12-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>1,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,43</t>
+          <t>-3,48; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 6,14</t>
+          <t>-0,78; 5,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,97</t>
+          <t>0,03; 5,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,18</t>
+          <t>-0,22; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,76</t>
+          <t>-0,37; 4,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,26</t>
+          <t>-0,48; 3,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,65</t>
+          <t>-1,47; 2,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,36</t>
+          <t>-0,06; 4,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,79</t>
+          <t>0,08; 3,57</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 73,43</t>
+          <t>-55,92; 62,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 167,57</t>
+          <t>-15,35; 159,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 189,77</t>
+          <t>-0,13; 168,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 685,49</t>
+          <t>-33,2; 629,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 739,01</t>
+          <t>-24,79; 633,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 466,22</t>
+          <t>-26,38; 576,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 103,48</t>
+          <t>-34,09; 102,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 159,52</t>
+          <t>-2,04; 178,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 147,89</t>
+          <t>1,61; 142,18</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,09</t>
+          <t>-2,16; 3,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,84</t>
+          <t>-1,74; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,94</t>
+          <t>0,88; 7,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,55</t>
+          <t>-0,98; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,63</t>
+          <t>-0,98; 3,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,57</t>
+          <t>-0,93; 2,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,2</t>
+          <t>-0,73; 3,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,6</t>
+          <t>-0,28; 3,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,08</t>
+          <t>0,94; 4,65</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105,84%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>105,49%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 136,54</t>
+          <t>-40,25; 129,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 148,61</t>
+          <t>-28,59; 146,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 255,77</t>
+          <t>12,98; 240,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 565,05</t>
+          <t>-53,37; 817,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 675,78</t>
+          <t>-59,14; 642,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 458,75</t>
+          <t>-38,16; 518,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 149,5</t>
+          <t>-18,95; 149,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 165,15</t>
+          <t>-8,35; 161,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,46; 245,56</t>
+          <t>20,47; 223,55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>4,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,12</t>
+          <t>2,07; 8,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,17</t>
+          <t>1,94; 8,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 6,42</t>
+          <t>2,01; 8,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,67</t>
+          <t>-6,85; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,48</t>
+          <t>-7,12; 4,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,11</t>
+          <t>-3,28; 7,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,89</t>
+          <t>0,69; 6,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,02</t>
+          <t>0,98; 6,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,6</t>
+          <t>1,94; 7,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,88; 203,44</t>
+          <t>29,53; 215,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,63; 208,02</t>
+          <t>27,8; 188,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 132,63</t>
+          <t>28,47; 196,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,27; 79,79</t>
+          <t>-63,55; 79,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 101,07</t>
+          <t>-69,97; 109,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,14; 145,25</t>
+          <t>-32,94; 159,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,42; 132,52</t>
+          <t>7,87; 134,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 132,17</t>
+          <t>12,54; 137,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 103,9</t>
+          <t>27,27; 157,54</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,06</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>2,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,69</t>
+          <t>-0,8; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,02</t>
+          <t>-0,17; 4,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,33</t>
+          <t>1,15; 5,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,07</t>
+          <t>-1,33; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,57</t>
+          <t>-2,51; 1,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,15</t>
+          <t>-0,96; 2,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,72</t>
+          <t>-0,47; 2,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,19</t>
+          <t>-0,98; 2,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,9</t>
+          <t>0,49; 3,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 56,37</t>
+          <t>-10,73; 58,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 64,14</t>
+          <t>-2,95; 67,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 83,6</t>
+          <t>13,48; 87,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 91,43</t>
+          <t>-24,7; 97,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 48,23</t>
+          <t>-49,5; 46,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 61,14</t>
+          <t>-17,53; 92,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 50,38</t>
+          <t>-6,79; 48,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 40,39</t>
+          <t>-13,75; 43,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 53,45</t>
+          <t>7,16; 65,04</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>4,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,75</t>
+          <t>-3,34; 3,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,79</t>
+          <t>0,56; 7,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,78</t>
+          <t>-2,18; 4,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,49</t>
+          <t>0,49; 6,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,68</t>
+          <t>1,24; 6,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,41</t>
+          <t>3,16; 8,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,76</t>
+          <t>0,28; 4,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,47</t>
+          <t>2,07; 6,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,96</t>
+          <t>2,13; 6,01</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>112,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 88,51</t>
+          <t>-40,37; 80,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,27; 168,12</t>
+          <t>4,31; 178,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 126,93</t>
+          <t>-24,73; 110,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,4; 174,81</t>
+          <t>6,26; 159,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,46; 171,74</t>
+          <t>15,93; 170,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,65; 192,36</t>
+          <t>45,37; 237,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,56; 107,11</t>
+          <t>3,47; 99,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>25,7; 147,32</t>
+          <t>28,79; 139,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,7; 131,26</t>
+          <t>31,53; 139,12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,67</t>
+          <t>0,42; 5,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,38</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,97</t>
+          <t>-0,4; 2,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,28</t>
+          <t>1,54; 6,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,5</t>
+          <t>0,6; 6,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,86</t>
+          <t>-1,49; 3,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,02</t>
+          <t>1,29; 5,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,29</t>
+          <t>0,61; 5,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,63</t>
+          <t>-1,32; 2,54</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174,08%</t>
+          <t>176,88%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,78; 83,82</t>
+          <t>13,47; 75,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,74; 75,07</t>
+          <t>5,35; 70,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 44,47</t>
+          <t>-13,15; 38,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,49; 80,9</t>
+          <t>13,06; 81,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,51; 74,97</t>
+          <t>6,83; 73,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 37,92</t>
+          <t>-14,9; 35,31</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,96</t>
+          <t>0,63; 3,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,92</t>
+          <t>1,55; 4,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,01</t>
+          <t>1,98; 4,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,74</t>
+          <t>1,17; 3,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,14</t>
+          <t>0,55; 2,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>0,28; 2,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,88</t>
+          <t>1,21; 2,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,13</t>
+          <t>1,48; 3,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,72</t>
+          <t>1,55; 3,07</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,52; 58,77</t>
+          <t>9,56; 61,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25,07; 76,14</t>
+          <t>25,01; 79,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,49; 79,28</t>
+          <t>31,48; 88,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16,57; 70,05</t>
+          <t>17,19; 64,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,85; 58,01</t>
+          <t>8,52; 55,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 35,3</t>
+          <t>4,48; 45,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,14; 52,79</t>
+          <t>19,47; 56,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,77; 57,69</t>
+          <t>23,93; 58,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,93; 49,4</t>
+          <t>24,55; 56,6</t>
         </is>
       </c>
     </row>
